--- a/04_Figures/F02_subtypes/c_data/F02_subtypes_source_data.xlsx
+++ b/04_Figures/F02_subtypes/c_data/F02_subtypes_source_data.xlsx
@@ -7,13 +7,140 @@
   </bookViews>
   <sheets>
     <sheet name="overview" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="metadata" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="cluster_phenotype_calibration" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="cluster_vs_null" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="cluster_vs_phenotype" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="null_false_positive_rate" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="metadata" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="59">
+  <si>
+    <t xml:space="preserve">sheet</t>
+  </si>
+  <si>
+    <t xml:space="preserve">cluster_phenotype_calibration</t>
+  </si>
+  <si>
+    <t xml:space="preserve">cluster_vs_null</t>
+  </si>
+  <si>
+    <t xml:space="preserve">cluster_vs_phenotype</t>
+  </si>
+  <si>
+    <t xml:space="preserve">null_false_positive_rate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">space</t>
+  </si>
+  <si>
+    <t xml:space="preserve">view</t>
+  </si>
+  <si>
+    <t xml:space="preserve">n_subjects</t>
+  </si>
+  <si>
+    <t xml:space="preserve">n_features</t>
+  </si>
+  <si>
+    <t xml:space="preserve">cluster_sizes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">n_bh</t>
+  </si>
+  <si>
+    <t xml:space="preserve">null_any_hit</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p_empirical</t>
+  </si>
+  <si>
+    <t xml:space="preserve">eigengenes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">baseline</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5/10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">training_change</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3/11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">proteins</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6/9</t>
+  </si>
+  <si>
+    <t xml:space="preserve">n_pc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">best_g</t>
+  </si>
+  <si>
+    <t xml:space="preserve">bic_gain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">null_gain_median</t>
+  </si>
+  <si>
+    <t xml:space="preserve">null_gain_q95</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phenotype</t>
+  </si>
+  <si>
+    <t xml:space="preserve">n</t>
+  </si>
+  <si>
+    <t xml:space="preserve">d</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p</t>
+  </si>
+  <si>
+    <t xml:space="preserve">bh</t>
+  </si>
+  <si>
+    <t xml:space="preserve">comp_hypertrophy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">d_fcsa_I</t>
+  </si>
+  <si>
+    <t xml:space="preserve">d_fcsa_II</t>
+  </si>
+  <si>
+    <t xml:space="preserve">d_fcsa_mixed</t>
+  </si>
+  <si>
+    <t xml:space="preserve">d_nfibre_mixed</t>
+  </si>
+  <si>
+    <t xml:space="preserve">d_nfibre_I</t>
+  </si>
+  <si>
+    <t xml:space="preserve">d_mcsa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">d_1rm_legpress</t>
+  </si>
+  <si>
+    <t xml:space="preserve">d_1rm_ext</t>
+  </si>
+  <si>
+    <t xml:space="preserve">volume_load</t>
+  </si>
+  <si>
+    <t xml:space="preserve">null_g_above_1</t>
+  </si>
   <si>
     <t xml:space="preserve">field</t>
   </si>
@@ -394,7 +521,33 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
-  <sheetData/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
 </worksheet>
@@ -407,74 +560,1429 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="B1" t="s">
-        <v>1</v>
+        <v>6</v>
+      </c>
+      <c r="C1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E1" t="s">
+        <v>9</v>
+      </c>
+      <c r="F1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G1" t="s">
+        <v>11</v>
+      </c>
+      <c r="H1" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="B2" t="s">
-        <v>3</v>
+        <v>14</v>
+      </c>
+      <c r="C2" t="n">
+        <v>15</v>
+      </c>
+      <c r="D2" t="n">
+        <v>12</v>
+      </c>
+      <c r="E2" t="s">
+        <v>15</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.0870870870870871</v>
+      </c>
+      <c r="H2" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="B3" t="s">
-        <v>5</v>
+        <v>16</v>
+      </c>
+      <c r="C3" t="n">
+        <v>14</v>
+      </c>
+      <c r="D3" t="n">
+        <v>12</v>
+      </c>
+      <c r="E3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.206206206206206</v>
+      </c>
+      <c r="H3" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="B4" t="s">
-        <v>7</v>
+        <v>14</v>
+      </c>
+      <c r="C4" t="n">
+        <v>15</v>
+      </c>
+      <c r="D4" t="n">
+        <v>500</v>
+      </c>
+      <c r="E4" t="s">
+        <v>19</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.0610610610610611</v>
+      </c>
+      <c r="H4" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="B5" t="s">
-        <v>9</v>
+        <v>16</v>
+      </c>
+      <c r="C5" t="n">
+        <v>14</v>
+      </c>
+      <c r="D5" t="n">
+        <v>500</v>
+      </c>
+      <c r="E5" t="s">
+        <v>17</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.193193193193193</v>
+      </c>
+      <c r="H5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D1" t="s">
+        <v>22</v>
+      </c>
+      <c r="E1" t="s">
+        <v>23</v>
+      </c>
+      <c r="F1" t="s">
+        <v>24</v>
+      </c>
+      <c r="G1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B2" t="n">
+        <v>2</v>
+      </c>
+      <c r="C2" t="n">
+        <v>4</v>
+      </c>
+      <c r="D2" t="n">
+        <v>8.49694800432783</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2" t="n">
+        <v>12.1117706044225</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.098</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s">
+        <v>13</v>
+      </c>
+      <c r="B3" t="n">
+        <v>3</v>
+      </c>
+      <c r="C3" t="n">
+        <v>4</v>
+      </c>
+      <c r="D3" t="n">
+        <v>6.86487733367557</v>
+      </c>
+      <c r="E3" t="n">
+        <v>2.94694233184273</v>
+      </c>
+      <c r="F3" t="n">
+        <v>29.219619296898</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.338</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s">
+        <v>13</v>
+      </c>
+      <c r="B4" t="n">
+        <v>4</v>
+      </c>
+      <c r="C4" t="n">
+        <v>4</v>
+      </c>
+      <c r="D4" t="n">
+        <v>36.7341213205336</v>
+      </c>
+      <c r="E4" t="n">
+        <v>8.80290079406581</v>
+      </c>
+      <c r="F4" t="n">
+        <v>77.1019120879345</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.191</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s">
+        <v>18</v>
+      </c>
+      <c r="B5" t="n">
+        <v>2</v>
+      </c>
+      <c r="C5" t="n">
+        <v>4</v>
+      </c>
+      <c r="D5" t="n">
+        <v>7.712641061277</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" t="n">
+        <v>13.6810448916788</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.123</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>10</v>
-      </c>
-      <c r="B6" t="s">
-        <v>11</v>
+        <v>18</v>
+      </c>
+      <c r="B6" t="n">
+        <v>3</v>
+      </c>
+      <c r="C6" t="n">
+        <v>2</v>
+      </c>
+      <c r="D6" t="n">
+        <v>3.66610234015815</v>
+      </c>
+      <c r="E6" t="n">
+        <v>2.37834236448214</v>
+      </c>
+      <c r="F6" t="n">
+        <v>27.7383674871727</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.443</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>12</v>
+        <v>18</v>
+      </c>
+      <c r="B7" t="n">
+        <v>4</v>
+      </c>
+      <c r="C7" t="n">
+        <v>2</v>
+      </c>
+      <c r="D7" t="n">
+        <v>3.89555307834223</v>
+      </c>
+      <c r="E7" t="n">
+        <v>9.4860388074294</v>
+      </c>
+      <c r="F7" t="n">
+        <v>84.3133638687243</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.613</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C1" t="s">
+        <v>25</v>
+      </c>
+      <c r="D1" t="s">
+        <v>26</v>
+      </c>
+      <c r="E1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1" t="s">
+        <v>28</v>
+      </c>
+      <c r="G1" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C2" t="s">
+        <v>30</v>
+      </c>
+      <c r="D2" t="n">
+        <v>15</v>
+      </c>
+      <c r="E2" t="n">
+        <v>-0.195517069892454</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.756316576530622</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.756316576530622</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s">
+        <v>13</v>
+      </c>
+      <c r="B3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C3" t="s">
+        <v>31</v>
+      </c>
+      <c r="D3" t="n">
+        <v>15</v>
+      </c>
+      <c r="E3" t="n">
+        <v>-0.464278506437067</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.376436619166006</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.756316576530622</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s">
+        <v>13</v>
+      </c>
+      <c r="B4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C4" t="s">
+        <v>32</v>
+      </c>
+      <c r="D4" t="n">
+        <v>15</v>
+      </c>
+      <c r="E4" t="n">
+        <v>-0.246532872814447</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.644113191363906</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.756316576530622</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s">
+        <v>13</v>
+      </c>
+      <c r="B5" t="s">
+        <v>14</v>
+      </c>
+      <c r="C5" t="s">
+        <v>33</v>
+      </c>
+      <c r="D5" t="n">
+        <v>15</v>
+      </c>
+      <c r="E5" t="n">
+        <v>-0.38691359284071</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.478086811768076</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.756316576530622</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s">
+        <v>13</v>
+      </c>
+      <c r="B6" t="s">
+        <v>14</v>
+      </c>
+      <c r="C6" t="s">
+        <v>34</v>
+      </c>
+      <c r="D6" t="n">
+        <v>15</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0.319144632538754</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.52184902222498</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.756316576530622</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s">
+        <v>13</v>
       </c>
       <c r="B7" t="s">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="C7" t="s">
+        <v>35</v>
+      </c>
+      <c r="D7" t="n">
+        <v>15</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0.44833953402757</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.407047280419133</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.756316576530622</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B8" t="s">
-        <v>15</v>
+        <v>14</v>
+      </c>
+      <c r="C8" t="s">
+        <v>36</v>
+      </c>
+      <c r="D8" t="n">
+        <v>15</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0.42565158783058</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.544581279611609</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.756316576530622</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="B9" t="s">
-        <v>17</v>
+        <v>14</v>
+      </c>
+      <c r="C9" t="s">
+        <v>37</v>
+      </c>
+      <c r="D9" t="n">
+        <v>15</v>
+      </c>
+      <c r="E9" t="n">
+        <v>-0.499976867065901</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.372731736368553</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.756316576530622</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="s">
+        <v>13</v>
+      </c>
+      <c r="B10" t="s">
+        <v>14</v>
+      </c>
+      <c r="C10" t="s">
+        <v>38</v>
+      </c>
+      <c r="D10" t="n">
+        <v>14</v>
+      </c>
+      <c r="E10" t="n">
+        <v>-0.581130331303537</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.333720751628611</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.756316576530622</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="s">
+        <v>13</v>
+      </c>
+      <c r="B11" t="s">
+        <v>14</v>
+      </c>
+      <c r="C11" t="s">
+        <v>39</v>
+      </c>
+      <c r="D11" t="n">
+        <v>15</v>
+      </c>
+      <c r="E11" t="n">
+        <v>-0.225919865075509</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.718489138165516</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.756316576530622</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="s">
+        <v>13</v>
+      </c>
+      <c r="B12" t="s">
+        <v>16</v>
+      </c>
+      <c r="C12" t="s">
+        <v>30</v>
+      </c>
+      <c r="D12" t="n">
+        <v>14</v>
+      </c>
+      <c r="E12" t="n">
+        <v>0.196097059226584</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0.737818334434404</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0.881927842614696</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="s">
+        <v>13</v>
+      </c>
+      <c r="B13" t="s">
+        <v>16</v>
+      </c>
+      <c r="C13" t="s">
+        <v>31</v>
+      </c>
+      <c r="D13" t="n">
+        <v>14</v>
+      </c>
+      <c r="E13" t="n">
+        <v>-0.246263890488598</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0.77384894783023</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0.881927842614696</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="s">
+        <v>13</v>
+      </c>
+      <c r="B14" t="s">
+        <v>16</v>
+      </c>
+      <c r="C14" t="s">
+        <v>32</v>
+      </c>
+      <c r="D14" t="n">
+        <v>14</v>
+      </c>
+      <c r="E14" t="n">
+        <v>-0.344824406086155</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0.681505033312131</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0.881927842614696</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="s">
+        <v>13</v>
+      </c>
+      <c r="B15" t="s">
+        <v>16</v>
+      </c>
+      <c r="C15" t="s">
+        <v>33</v>
+      </c>
+      <c r="D15" t="n">
+        <v>14</v>
+      </c>
+      <c r="E15" t="n">
+        <v>-0.346530571007088</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0.667408432247422</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0.881927842614696</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="s">
+        <v>13</v>
+      </c>
+      <c r="B16" t="s">
+        <v>16</v>
+      </c>
+      <c r="C16" t="s">
+        <v>34</v>
+      </c>
+      <c r="D16" t="n">
+        <v>14</v>
+      </c>
+      <c r="E16" t="n">
+        <v>0.288867623709559</v>
+      </c>
+      <c r="F16" t="n">
+        <v>0.643349102474684</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0.881927842614696</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="s">
+        <v>13</v>
+      </c>
+      <c r="B17" t="s">
+        <v>16</v>
+      </c>
+      <c r="C17" t="s">
+        <v>35</v>
+      </c>
+      <c r="D17" t="n">
+        <v>14</v>
+      </c>
+      <c r="E17" t="n">
+        <v>0.371547842574021</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0.603613067980544</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0.881927842614696</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="s">
+        <v>13</v>
+      </c>
+      <c r="B18" t="s">
+        <v>16</v>
+      </c>
+      <c r="C18" t="s">
+        <v>36</v>
+      </c>
+      <c r="D18" t="n">
+        <v>14</v>
+      </c>
+      <c r="E18" t="n">
+        <v>1.13511792457685</v>
+      </c>
+      <c r="F18" t="n">
+        <v>0.147829796857118</v>
+      </c>
+      <c r="G18" t="n">
+        <v>0.881927842614696</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="s">
+        <v>13</v>
+      </c>
+      <c r="B19" t="s">
+        <v>16</v>
+      </c>
+      <c r="C19" t="s">
+        <v>37</v>
+      </c>
+      <c r="D19" t="n">
+        <v>14</v>
+      </c>
+      <c r="E19" t="n">
+        <v>-0.173135358462349</v>
+      </c>
+      <c r="F19" t="n">
+        <v>0.692470271260536</v>
+      </c>
+      <c r="G19" t="n">
+        <v>0.881927842614696</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="s">
+        <v>13</v>
+      </c>
+      <c r="B20" t="s">
+        <v>16</v>
+      </c>
+      <c r="C20" t="s">
+        <v>38</v>
+      </c>
+      <c r="D20" t="n">
+        <v>13</v>
+      </c>
+      <c r="E20" t="n">
+        <v>0.312447449233466</v>
+      </c>
+      <c r="F20" t="n">
+        <v>0.793735058353226</v>
+      </c>
+      <c r="G20" t="n">
+        <v>0.881927842614696</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="s">
+        <v>18</v>
+      </c>
+      <c r="B21" t="s">
+        <v>16</v>
+      </c>
+      <c r="C21" t="s">
+        <v>30</v>
+      </c>
+      <c r="D21" t="n">
+        <v>14</v>
+      </c>
+      <c r="E21" t="n">
+        <v>0.196097059226584</v>
+      </c>
+      <c r="F21" t="n">
+        <v>0.737818334434404</v>
+      </c>
+      <c r="G21" t="n">
+        <v>0.881927842614696</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="s">
+        <v>18</v>
+      </c>
+      <c r="B22" t="s">
+        <v>16</v>
+      </c>
+      <c r="C22" t="s">
+        <v>31</v>
+      </c>
+      <c r="D22" t="n">
+        <v>14</v>
+      </c>
+      <c r="E22" t="n">
+        <v>-0.246263890488598</v>
+      </c>
+      <c r="F22" t="n">
+        <v>0.77384894783023</v>
+      </c>
+      <c r="G22" t="n">
+        <v>0.881927842614696</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="s">
+        <v>18</v>
+      </c>
+      <c r="B23" t="s">
+        <v>16</v>
+      </c>
+      <c r="C23" t="s">
+        <v>32</v>
+      </c>
+      <c r="D23" t="n">
+        <v>14</v>
+      </c>
+      <c r="E23" t="n">
+        <v>-0.344824406086155</v>
+      </c>
+      <c r="F23" t="n">
+        <v>0.681505033312131</v>
+      </c>
+      <c r="G23" t="n">
+        <v>0.881927842614696</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="s">
+        <v>18</v>
+      </c>
+      <c r="B24" t="s">
+        <v>16</v>
+      </c>
+      <c r="C24" t="s">
+        <v>33</v>
+      </c>
+      <c r="D24" t="n">
+        <v>14</v>
+      </c>
+      <c r="E24" t="n">
+        <v>-0.346530571007088</v>
+      </c>
+      <c r="F24" t="n">
+        <v>0.667408432247422</v>
+      </c>
+      <c r="G24" t="n">
+        <v>0.881927842614696</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="s">
+        <v>18</v>
+      </c>
+      <c r="B25" t="s">
+        <v>16</v>
+      </c>
+      <c r="C25" t="s">
+        <v>34</v>
+      </c>
+      <c r="D25" t="n">
+        <v>14</v>
+      </c>
+      <c r="E25" t="n">
+        <v>0.288867623709559</v>
+      </c>
+      <c r="F25" t="n">
+        <v>0.643349102474684</v>
+      </c>
+      <c r="G25" t="n">
+        <v>0.881927842614696</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="s">
+        <v>18</v>
+      </c>
+      <c r="B26" t="s">
+        <v>16</v>
+      </c>
+      <c r="C26" t="s">
+        <v>35</v>
+      </c>
+      <c r="D26" t="n">
+        <v>14</v>
+      </c>
+      <c r="E26" t="n">
+        <v>0.371547842574021</v>
+      </c>
+      <c r="F26" t="n">
+        <v>0.603613067980544</v>
+      </c>
+      <c r="G26" t="n">
+        <v>0.881927842614696</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="s">
+        <v>18</v>
+      </c>
+      <c r="B27" t="s">
+        <v>16</v>
+      </c>
+      <c r="C27" t="s">
+        <v>36</v>
+      </c>
+      <c r="D27" t="n">
+        <v>14</v>
+      </c>
+      <c r="E27" t="n">
+        <v>1.13511792457685</v>
+      </c>
+      <c r="F27" t="n">
+        <v>0.147829796857118</v>
+      </c>
+      <c r="G27" t="n">
+        <v>0.881927842614696</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="s">
+        <v>18</v>
+      </c>
+      <c r="B28" t="s">
+        <v>16</v>
+      </c>
+      <c r="C28" t="s">
+        <v>37</v>
+      </c>
+      <c r="D28" t="n">
+        <v>14</v>
+      </c>
+      <c r="E28" t="n">
+        <v>-0.173135358462349</v>
+      </c>
+      <c r="F28" t="n">
+        <v>0.692470271260536</v>
+      </c>
+      <c r="G28" t="n">
+        <v>0.881927842614696</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="s">
+        <v>18</v>
+      </c>
+      <c r="B29" t="s">
+        <v>16</v>
+      </c>
+      <c r="C29" t="s">
+        <v>38</v>
+      </c>
+      <c r="D29" t="n">
+        <v>13</v>
+      </c>
+      <c r="E29" t="n">
+        <v>0.312447449233466</v>
+      </c>
+      <c r="F29" t="n">
+        <v>0.793735058353226</v>
+      </c>
+      <c r="G29" t="n">
+        <v>0.881927842614696</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="s">
+        <v>13</v>
+      </c>
+      <c r="B30" t="s">
+        <v>16</v>
+      </c>
+      <c r="C30" t="s">
+        <v>39</v>
+      </c>
+      <c r="D30" t="n">
+        <v>14</v>
+      </c>
+      <c r="E30" t="n">
+        <v>0.0799767522514812</v>
+      </c>
+      <c r="F30" t="n">
+        <v>0.924436235879662</v>
+      </c>
+      <c r="G30" t="n">
+        <v>0.924436235879662</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="s">
+        <v>18</v>
+      </c>
+      <c r="B31" t="s">
+        <v>16</v>
+      </c>
+      <c r="C31" t="s">
+        <v>39</v>
+      </c>
+      <c r="D31" t="n">
+        <v>14</v>
+      </c>
+      <c r="E31" t="n">
+        <v>0.0799767522514812</v>
+      </c>
+      <c r="F31" t="n">
+        <v>0.924436235879662</v>
+      </c>
+      <c r="G31" t="n">
+        <v>0.924436235879662</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="s">
+        <v>18</v>
+      </c>
+      <c r="B32" t="s">
+        <v>14</v>
+      </c>
+      <c r="C32" t="s">
+        <v>30</v>
+      </c>
+      <c r="D32" t="n">
+        <v>15</v>
+      </c>
+      <c r="E32" t="n">
+        <v>0.00587476172161181</v>
+      </c>
+      <c r="F32" t="n">
+        <v>0.99179934066967</v>
+      </c>
+      <c r="G32" t="n">
+        <v>0.99179934066967</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="s">
+        <v>18</v>
+      </c>
+      <c r="B33" t="s">
+        <v>14</v>
+      </c>
+      <c r="C33" t="s">
+        <v>31</v>
+      </c>
+      <c r="D33" t="n">
+        <v>15</v>
+      </c>
+      <c r="E33" t="n">
+        <v>-0.299989531602491</v>
+      </c>
+      <c r="F33" t="n">
+        <v>0.560641061567135</v>
+      </c>
+      <c r="G33" t="n">
+        <v>0.99179934066967</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="s">
+        <v>18</v>
+      </c>
+      <c r="B34" t="s">
+        <v>14</v>
+      </c>
+      <c r="C34" t="s">
+        <v>32</v>
+      </c>
+      <c r="D34" t="n">
+        <v>15</v>
+      </c>
+      <c r="E34" t="n">
+        <v>-0.192330592829621</v>
+      </c>
+      <c r="F34" t="n">
+        <v>0.707518766920803</v>
+      </c>
+      <c r="G34" t="n">
+        <v>0.99179934066967</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="s">
+        <v>18</v>
+      </c>
+      <c r="B35" t="s">
+        <v>14</v>
+      </c>
+      <c r="C35" t="s">
+        <v>33</v>
+      </c>
+      <c r="D35" t="n">
+        <v>15</v>
+      </c>
+      <c r="E35" t="n">
+        <v>-0.291138195470892</v>
+      </c>
+      <c r="F35" t="n">
+        <v>0.575420165726677</v>
+      </c>
+      <c r="G35" t="n">
+        <v>0.99179934066967</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="s">
+        <v>18</v>
+      </c>
+      <c r="B36" t="s">
+        <v>14</v>
+      </c>
+      <c r="C36" t="s">
+        <v>34</v>
+      </c>
+      <c r="D36" t="n">
+        <v>15</v>
+      </c>
+      <c r="E36" t="n">
+        <v>0.0572196634623467</v>
+      </c>
+      <c r="F36" t="n">
+        <v>0.911319468447522</v>
+      </c>
+      <c r="G36" t="n">
+        <v>0.99179934066967</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="s">
+        <v>18</v>
+      </c>
+      <c r="B37" t="s">
+        <v>14</v>
+      </c>
+      <c r="C37" t="s">
+        <v>35</v>
+      </c>
+      <c r="D37" t="n">
+        <v>15</v>
+      </c>
+      <c r="E37" t="n">
+        <v>0.199639405303523</v>
+      </c>
+      <c r="F37" t="n">
+        <v>0.707859611668704</v>
+      </c>
+      <c r="G37" t="n">
+        <v>0.99179934066967</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="s">
+        <v>18</v>
+      </c>
+      <c r="B38" t="s">
+        <v>14</v>
+      </c>
+      <c r="C38" t="s">
+        <v>36</v>
+      </c>
+      <c r="D38" t="n">
+        <v>15</v>
+      </c>
+      <c r="E38" t="n">
+        <v>0.635562867294494</v>
+      </c>
+      <c r="F38" t="n">
+        <v>0.297068472640749</v>
+      </c>
+      <c r="G38" t="n">
+        <v>0.99179934066967</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="s">
+        <v>18</v>
+      </c>
+      <c r="B39" t="s">
+        <v>14</v>
+      </c>
+      <c r="C39" t="s">
+        <v>37</v>
+      </c>
+      <c r="D39" t="n">
+        <v>15</v>
+      </c>
+      <c r="E39" t="n">
+        <v>-0.617255391439385</v>
+      </c>
+      <c r="F39" t="n">
+        <v>0.235220343095275</v>
+      </c>
+      <c r="G39" t="n">
+        <v>0.99179934066967</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="s">
+        <v>18</v>
+      </c>
+      <c r="B40" t="s">
+        <v>14</v>
+      </c>
+      <c r="C40" t="s">
+        <v>38</v>
+      </c>
+      <c r="D40" t="n">
+        <v>14</v>
+      </c>
+      <c r="E40" t="n">
+        <v>-0.399527102771182</v>
+      </c>
+      <c r="F40" t="n">
+        <v>0.479270688369006</v>
+      </c>
+      <c r="G40" t="n">
+        <v>0.99179934066967</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="s">
+        <v>18</v>
+      </c>
+      <c r="B41" t="s">
+        <v>14</v>
+      </c>
+      <c r="C41" t="s">
+        <v>39</v>
+      </c>
+      <c r="D41" t="n">
+        <v>15</v>
+      </c>
+      <c r="E41" t="n">
+        <v>-0.0753133825863906</v>
+      </c>
+      <c r="F41" t="n">
+        <v>0.894066394056787</v>
+      </c>
+      <c r="G41" t="n">
+        <v>0.99179934066967</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C1" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B2" t="n">
+        <v>2</v>
+      </c>
+      <c r="C2" t="n">
+        <v>0.468468468468468</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s">
+        <v>13</v>
+      </c>
+      <c r="B3" t="n">
+        <v>3</v>
+      </c>
+      <c r="C3" t="n">
+        <v>0.644644644644645</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s">
+        <v>13</v>
+      </c>
+      <c r="B4" t="n">
+        <v>4</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0.76976976976977</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s">
+        <v>18</v>
+      </c>
+      <c r="B5" t="n">
+        <v>2</v>
+      </c>
+      <c r="C5" t="n">
+        <v>0.481481481481481</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s">
+        <v>18</v>
+      </c>
+      <c r="B6" t="n">
+        <v>3</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0.636636636636637</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s">
+        <v>18</v>
+      </c>
+      <c r="B7" t="n">
+        <v>4</v>
+      </c>
+      <c r="C7" t="n">
+        <v>0.740740740740741</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s">
+        <v>41</v>
+      </c>
+      <c r="B1" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s">
+        <v>43</v>
+      </c>
+      <c r="B2" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s">
+        <v>45</v>
+      </c>
+      <c r="B3" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s">
+        <v>47</v>
+      </c>
+      <c r="B4" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s">
+        <v>49</v>
+      </c>
+      <c r="B5" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s">
+        <v>51</v>
+      </c>
+      <c r="B6" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s">
+        <v>53</v>
+      </c>
+      <c r="B7" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s">
+        <v>55</v>
+      </c>
+      <c r="B8" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="s">
+        <v>57</v>
+      </c>
+      <c r="B9" t="s">
+        <v>58</v>
       </c>
     </row>
   </sheetData>
